--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5FA77A-E14D-5844-919A-57ED669F384F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9886E6-B025-214D-8FC0-DE448323DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1565,8 +1565,8 @@
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>67</v>
+      <c r="B47" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9886E6-B025-214D-8FC0-DE448323DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DDB363-71BA-CB40-B0C4-DE97043AFF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30400" yWindow="-21760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -335,9 +335,6 @@
     <t>Trail</t>
   </si>
   <si>
-    <t>https://www.specialized.com/us/en/chisel-hardtail-frameset/p/4221776?color=5382719-4221776</t>
-  </si>
-  <si>
     <t>bb_height</t>
   </si>
   <si>
@@ -393,6 +390,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.specialized.com/us/en/shop/bikes/mountain-bikes/cross-country-mountain-bikes/chisel?search=chiselhardtail-chiselhardtail&amp;filter=15x1322712467z15x1322712467</t>
+  </si>
+  <si>
+    <t>https://assets.specialized.com/i/specialized/91725-50_CHISEL-HT-COMP-GLOSS-METALLIC-DEEP-MARINE---WHITE_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
   </si>
 </sst>
 </file>
@@ -805,7 +808,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -813,7 +821,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -913,7 +921,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>82</v>
@@ -936,7 +944,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>83</v>
@@ -1189,7 +1197,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>94</v>
@@ -1448,10 +1456,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="D36" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1463,7 +1471,7 @@
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>78</v>
@@ -1472,13 +1480,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="D38" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>69</v>
@@ -1486,13 +1494,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>70</v>
@@ -1500,13 +1508,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>71</v>
@@ -1520,7 +1528,7 @@
         <v>75</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>74</v>
@@ -1531,7 +1539,7 @@
         <v>32</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1615,7 +1623,7 @@
         <v>45</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1751,7 +1759,7 @@
         <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DDB363-71BA-CB40-B0C4-DE97043AFF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C50FAD-A928-1F4B-8C64-8B1CBE9A8027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30400" yWindow="-21760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>https://assets.specialized.com/i/specialized/91725-50_CHISEL-HT-COMP-GLOSS-METALLIC-DEEP-MARINE---WHITE_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
+  </si>
+  <si>
+    <t>threaded</t>
   </si>
 </sst>
 </file>
@@ -1607,6 +1610,9 @@
       <c r="A52" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B52" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
@@ -1617,6 +1623,9 @@
       <c r="A54" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="B54" s="1">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
@@ -1747,6 +1756,9 @@
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1899</v>
       </c>
     </row>
     <row r="74" spans="1:2">

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C50FAD-A928-1F4B-8C64-8B1CBE9A8027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2352F679-D547-DF41-B511-DD1E2B296671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2352F679-D547-DF41-B511-DD1E2B296671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189138C9-4883-BF41-AD25-53EF9DD10EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>threaded</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Morgan Hill, California, USA</t>
   </si>
 </sst>
 </file>
@@ -766,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1774,6 +1780,14 @@
         <v>118</v>
       </c>
     </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189138C9-4883-BF41-AD25-53EF9DD10EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278B257-5D6C-BB46-83FC-E5F0FF60DF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -405,6 +405,24 @@
   </si>
   <si>
     <t>Morgan Hill, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -772,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1614,177 +1632,207 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="1">
-        <v>30.9</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" s="1">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B60" s="1">
+        <v>30.9</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>67</v>
+        <v>46</v>
+      </c>
+      <c r="B62" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="1">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B71" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B72" s="1">
-        <v>1799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B73" s="1">
-        <v>1899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>118</v>
+        <v>59</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>123</v>
       </c>
     </row>

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C278B257-5D6C-BB46-83FC-E5F0FF60DF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7358E26-F7F7-D144-8EB4-0C053DD285CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,48 +1755,30 @@
       <c r="A72" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B72" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B73" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B74" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B76" s="1">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B77" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">

--- a/data/gravel/Specialized Chisel 2025.xlsx
+++ b/data/gravel/Specialized Chisel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7358E26-F7F7-D144-8EB4-0C053DD285CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13A6E43-D91A-9645-9043-DC7DDD97EF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -386,9 +386,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>a8:g35</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -423,6 +420,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g37</t>
   </si>
 </sst>
 </file>
@@ -790,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -835,12 +841,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -848,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1362,460 +1368,488 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+        <v>129</v>
+      </c>
+      <c r="C30" s="4">
+        <v>80</v>
+      </c>
+      <c r="D30" s="4">
+        <v>100</v>
+      </c>
       <c r="E30" s="4">
-        <v>1350</v>
-      </c>
-      <c r="F30" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="F30" s="4">
+        <v>100</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4">
-        <v>700</v>
-      </c>
-      <c r="D31" s="4">
-        <v>700</v>
-      </c>
-      <c r="E31" s="4">
-        <v>700</v>
-      </c>
-      <c r="F31" s="4">
-        <v>700</v>
-      </c>
-      <c r="G31" s="4">
-        <v>700</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4">
+        <v>1350</v>
+      </c>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="4">
+        <v>700</v>
+      </c>
+      <c r="D33" s="4">
+        <v>700</v>
+      </c>
+      <c r="E33" s="4">
+        <v>700</v>
+      </c>
+      <c r="F33" s="4">
+        <v>700</v>
+      </c>
+      <c r="G33" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C34" s="4">
         <f>2.35*25.4</f>
         <v>59.69</v>
       </c>
-      <c r="D32" s="4">
-        <f t="shared" ref="D32:G32" si="0">2.35*25.4</f>
+      <c r="D34" s="4">
+        <f t="shared" ref="D34:G34" si="0">2.35*25.4</f>
         <v>59.69</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E34" s="4">
         <f t="shared" si="0"/>
         <v>59.69</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F34" s="4">
         <f t="shared" si="0"/>
         <v>59.69</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G34" s="4">
         <f t="shared" si="0"/>
         <v>59.69</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1" t="s">
+    <row r="35" spans="1:7">
+      <c r="A35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C35" s="4">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D33" s="4">
-        <f t="shared" ref="D33:G33" si="1">2.4*25.4</f>
+      <c r="D35" s="4">
+        <f t="shared" ref="D35:G35" si="1">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E35" s="4">
         <f t="shared" si="1"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F35" s="4">
         <f t="shared" si="1"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G35" s="4">
         <f t="shared" si="1"/>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1" t="s">
+    <row r="36" spans="1:7">
+      <c r="A36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C36" s="4">
         <v>148</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D36" s="4">
         <v>158</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E36" s="4">
         <v>165</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F36" s="4">
         <v>178</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G36" s="4">
         <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="4">
-        <v>155</v>
-      </c>
-      <c r="D35" s="4">
-        <v>165</v>
-      </c>
-      <c r="E35" s="4">
-        <v>178</v>
-      </c>
-      <c r="F35" s="4">
-        <v>185</v>
-      </c>
-      <c r="G35" s="4">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="D36" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="4">
+        <v>155</v>
+      </c>
+      <c r="D37" s="4">
+        <v>165</v>
+      </c>
+      <c r="E37" s="4">
+        <v>178</v>
+      </c>
+      <c r="F37" s="4">
+        <v>185</v>
+      </c>
+      <c r="G37" s="4">
+        <v>193</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>69</v>
+      <c r="D38" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B46" s="1">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="1">
-        <v>100</v>
-      </c>
-    </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="1">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B48" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="B49" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="1">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="1">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>124</v>
+        <v>40</v>
+      </c>
+      <c r="B52" s="1">
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="B53" s="1">
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="1">
-        <v>30.9</v>
+        <v>42</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B62" s="1">
-        <v>36</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="B64" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B71" s="1">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78" s="1">
-        <v>1799</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1899</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B80" s="1">
+        <v>1799</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>118</v>
+        <v>63</v>
+      </c>
+      <c r="B81" s="1">
+        <v>1899</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
